--- a/DRL_Routing_Summary_stochastic_sigma10%.xlsx
+++ b/DRL_Routing_Summary_stochastic_sigma10%.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9faf7a5fe1343c6/Desktop/Maestria/Tesis MSc/RoutingModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_8B418FE74D0C50833209DF5739358AD3C21CA19D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E47478A1-5B33-47C2-ABA3-18613AB61260}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{C0D3D6B9-674E-4CA0-8C4B-9A72A3B413BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Node Results" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
   <si>
     <t>Start Node</t>
   </si>
@@ -113,7 +113,7 @@
     <t>LNS Gap (%)</t>
   </si>
   <si>
-    <t>[0, 3, 2, 1, 7, 0]</t>
+    <t>[0, 3, 2, 1, 0]</t>
   </si>
   <si>
     <t>Optimal</t>
@@ -125,10 +125,7 @@
     <t>[0, 7, 9, 8, 6, 0]</t>
   </si>
   <si>
-    <t>[0, 3, 1, 2, 4, 0]</t>
-  </si>
-  <si>
-    <t>[1, 3, 2, 5, 7, 1]</t>
+    <t>[1, 4, 3, 2, 1]</t>
   </si>
   <si>
     <t>[1, 2, 3, 5, 4, 1]</t>
@@ -140,7 +137,7 @@
     <t>[1, 2, 7, 5, 3, 1]</t>
   </si>
   <si>
-    <t>[2, 3, 1, 4, 5, 2]</t>
+    <t>[2, 3, 1, 4, 2]</t>
   </si>
   <si>
     <t>[2, 3, 5, 4, 1, 2]</t>
@@ -149,10 +146,10 @@
     <t>[2, 3, 1, 4, 7, 2]</t>
   </si>
   <si>
-    <t>[2, 3, 0, 4, 1, 2]</t>
-  </si>
-  <si>
-    <t>[3, 7, 9, 5, 1, 3]</t>
+    <t>[2, 4, 5, 0, 1, 2]</t>
+  </si>
+  <si>
+    <t>[3, 2, 4, 1, 3]</t>
   </si>
   <si>
     <t>[3, 5, 4, 1, 2, 3]</t>
@@ -164,10 +161,10 @@
     <t>[3, 1, 4, 7, 2, 3]</t>
   </si>
   <si>
-    <t>[3, 0, 1, 4, 5, 3]</t>
-  </si>
-  <si>
-    <t>[4, 5, 3, 7, 9, 4]</t>
+    <t>[3, 1, 2, 4, 5, 3]</t>
+  </si>
+  <si>
+    <t>[4, 3, 2, 1, 4]</t>
   </si>
   <si>
     <t>[4, 1, 2, 3, 5, 4]</t>
@@ -176,10 +173,7 @@
     <t>[4, 2, 3, 1, 7, 4]</t>
   </si>
   <si>
-    <t>[4, 0, 3, 1, 2, 4]</t>
-  </si>
-  <si>
-    <t>[5, 3, 2, 1, 7, 5]</t>
+    <t>[5, 3, 2, 1, 5]</t>
   </si>
   <si>
     <t>[5, 4, 1, 2, 3, 5]</t>
@@ -191,7 +185,7 @@
     <t>[5, 3, 1, 2, 4, 5]</t>
   </si>
   <si>
-    <t>[6, 8, 9, 4, 1, 6]</t>
+    <t>[6, 2, 1, 3, 0, 6]</t>
   </si>
   <si>
     <t>[6, 1, 2, 3, 8, 6]</t>
@@ -203,10 +197,10 @@
     <t>[6, 2, 7, 9, 8, 6]</t>
   </si>
   <si>
-    <t>[6, 5, 3, 1, 2, 6]</t>
-  </si>
-  <si>
-    <t>[7, 9, 1, 3, 4, 7]</t>
+    <t>[6, 1, 2, 4, 8, 6]</t>
+  </si>
+  <si>
+    <t>[7, 1, 3, 2, 4, 7]</t>
   </si>
   <si>
     <t>[7, 2, 3, 1, 4, 7]</t>
@@ -215,10 +209,7 @@
     <t>[7, 9, 8, 6, 2, 7]</t>
   </si>
   <si>
-    <t>[7, 5, 3, 1, 2, 7]</t>
-  </si>
-  <si>
-    <t>[8, 9, 2, 1, 4, 8]</t>
+    <t>[8, 4, 2, 1, 3, 8]</t>
   </si>
   <si>
     <t>[8, 2, 3, 1, 4, 8]</t>
@@ -230,7 +221,10 @@
     <t>[8, 6, 9, 2, 7, 8]</t>
   </si>
   <si>
-    <t>[9, 7, 1, 3, 4, 9]</t>
+    <t>[8, 2, 3, 1, 7, 8]</t>
+  </si>
+  <si>
+    <t>[9, 1, 3, 2, 4, 9]</t>
   </si>
   <si>
     <t>[9, 2, 3, 1, 4, 9]</t>
@@ -630,12 +624,9 @@
   <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -738,19 +729,19 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>826</v>
+        <v>1324</v>
       </c>
       <c r="D2">
-        <v>41.6</v>
+        <v>22.7</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>819.09634304376641</v>
+        <v>1318.016067814985</v>
       </c>
       <c r="G2">
-        <v>182.4097273774243</v>
+        <v>63.156732115162782</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -798,19 +789,19 @@
         <v>31</v>
       </c>
       <c r="W2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X2">
-        <v>1444</v>
+        <v>1515</v>
       </c>
       <c r="Y2">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Z2" t="b">
         <v>1</v>
       </c>
       <c r="AA2">
-        <v>45.478547854785482</v>
+        <v>12.60726072607261</v>
       </c>
       <c r="AB2">
         <v>103.03630363036309</v>
@@ -819,7 +810,7 @@
         <v>103.03630363036309</v>
       </c>
       <c r="AD2">
-        <v>4.6864686468646868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
@@ -827,22 +818,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>642</v>
+        <v>1403</v>
       </c>
       <c r="D3">
-        <v>40.799999999999997</v>
+        <v>24.1</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>648.64952236800559</v>
+        <v>1398.9826789306401</v>
       </c>
       <c r="G3">
-        <v>150.8276319609121</v>
+        <v>64.285124433086423</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -851,7 +842,7 @@
         <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K3">
         <v>1674</v>
@@ -863,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O3">
         <v>861</v>
@@ -875,7 +866,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S3">
         <v>873</v>
@@ -890,7 +881,7 @@
         <v>31</v>
       </c>
       <c r="W3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X3">
         <v>1674</v>
@@ -902,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="AA3">
-        <v>61.648745519713273</v>
+        <v>16.188769414575869</v>
       </c>
       <c r="AB3">
         <v>48.566308243727597</v>
@@ -919,22 +910,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4">
-        <v>1340</v>
+        <v>1365</v>
       </c>
       <c r="D4">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1306.6530849156461</v>
+        <v>1353.2805341538501</v>
       </c>
       <c r="G4">
-        <v>191.1267865669266</v>
+        <v>66.17341855268846</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -943,7 +934,7 @@
         <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K4">
         <v>1674</v>
@@ -955,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O4">
         <v>957</v>
@@ -967,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S4">
         <v>957</v>
@@ -982,19 +973,19 @@
         <v>31</v>
       </c>
       <c r="W4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X4">
-        <v>1515</v>
+        <v>1156</v>
       </c>
       <c r="Y4">
-        <v>29</v>
+        <v>21.5</v>
       </c>
       <c r="Z4" t="b">
         <v>1</v>
       </c>
       <c r="AA4">
-        <v>19.952210274790922</v>
+        <v>18.458781362007169</v>
       </c>
       <c r="AB4">
         <v>42.831541218637987</v>
@@ -1003,7 +994,7 @@
         <v>42.831541218637987</v>
       </c>
       <c r="AD4">
-        <v>9.4982078853046588</v>
+        <v>30.943847072879329</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
@@ -1011,22 +1002,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>1475</v>
       </c>
       <c r="D5">
-        <v>37.1</v>
+        <v>29.9</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>25.868613170190269</v>
+        <v>1486.484714098588</v>
       </c>
       <c r="G5">
-        <v>178.13903180141969</v>
+        <v>71.580912833110403</v>
       </c>
       <c r="H5">
         <v>100</v>
@@ -1035,7 +1026,7 @@
         <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K5">
         <v>1674</v>
@@ -1047,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O5">
         <v>694</v>
@@ -1059,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S5">
         <v>957</v>
@@ -1074,19 +1065,19 @@
         <v>31</v>
       </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X5">
-        <v>1187</v>
+        <v>1610</v>
       </c>
       <c r="Y5">
-        <v>25.6</v>
+        <v>30.8</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
       </c>
       <c r="AA5">
-        <v>99.044205495818389</v>
+        <v>11.88769414575866</v>
       </c>
       <c r="AB5">
         <v>58.542413381123062</v>
@@ -1095,7 +1086,7 @@
         <v>42.831541218637987</v>
       </c>
       <c r="AD5">
-        <v>29.091995221027481</v>
+        <v>3.8231780167264038</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
@@ -1103,22 +1094,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>1403</v>
       </c>
       <c r="D6">
-        <v>41.3</v>
+        <v>24.1</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>49.691644960115561</v>
+        <v>1409.78431589913</v>
       </c>
       <c r="G6">
-        <v>155.130661165677</v>
+        <v>51.551823166942803</v>
       </c>
       <c r="H6">
         <v>100</v>
@@ -1127,7 +1118,7 @@
         <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6">
         <v>1674</v>
@@ -1139,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O6">
         <v>919</v>
@@ -1151,7 +1142,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6">
         <v>919</v>
@@ -1166,19 +1157,19 @@
         <v>31</v>
       </c>
       <c r="W6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="X6">
-        <v>1444</v>
+        <v>1674</v>
       </c>
       <c r="Y6">
-        <v>29.2</v>
+        <v>30.8</v>
       </c>
       <c r="Z6" t="b">
         <v>1</v>
       </c>
       <c r="AA6">
-        <v>99.044205495818389</v>
+        <v>16.188769414575869</v>
       </c>
       <c r="AB6">
         <v>45.101553166069287</v>
@@ -1187,7 +1178,7 @@
         <v>45.101553166069287</v>
       </c>
       <c r="AD6">
-        <v>13.739545997610509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
@@ -1195,22 +1186,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>861</v>
+        <v>1351</v>
       </c>
       <c r="D7">
-        <v>41.3</v>
+        <v>22.9</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>856.71255505919873</v>
+        <v>1338.552168851973</v>
       </c>
       <c r="G7">
-        <v>186.98378720267641</v>
+        <v>58.267087661206773</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -1219,7 +1210,7 @@
         <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K7">
         <v>1674</v>
@@ -1231,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O7">
         <v>1229</v>
@@ -1243,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S7">
         <v>1610</v>
@@ -1258,10 +1249,10 @@
         <v>31</v>
       </c>
       <c r="W7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="X7">
-        <v>1610</v>
+        <v>1674</v>
       </c>
       <c r="Y7">
         <v>30.8</v>
@@ -1270,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="AA7">
-        <v>48.566308243727597</v>
+        <v>19.29510155316607</v>
       </c>
       <c r="AB7">
         <v>26.583034647550779</v>
@@ -1279,7 +1270,7 @@
         <v>3.8231780167264038</v>
       </c>
       <c r="AD7">
-        <v>3.8231780167264038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
@@ -1287,22 +1278,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="D8">
-        <v>47.6</v>
+        <v>53.6</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>44.671827112289449</v>
+        <v>385.15986919386188</v>
       </c>
       <c r="G8">
-        <v>199.33571051079809</v>
+        <v>54.4177120811094</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1311,7 +1302,7 @@
         <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>518</v>
@@ -1323,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O8">
         <v>-481</v>
@@ -1335,7 +1326,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="S8">
         <v>-84</v>
@@ -1350,19 +1341,19 @@
         <v>31</v>
       </c>
       <c r="W8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X8">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="Y8">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="Z8" t="b">
         <v>1</v>
       </c>
       <c r="AA8">
-        <v>84.749034749034749</v>
+        <v>26.44787644787645</v>
       </c>
       <c r="AB8">
         <v>192.85714285714289</v>
@@ -1371,7 +1362,7 @@
         <v>116.2162162162162</v>
       </c>
       <c r="AD8">
-        <v>15.057915057915061</v>
+        <v>11.389961389961391</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
@@ -1379,22 +1370,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>372</v>
+        <v>919</v>
       </c>
       <c r="D9">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>371.20345656994749</v>
+        <v>920.03428889936708</v>
       </c>
       <c r="G9">
-        <v>201.51105693726339</v>
+        <v>74.151336908880822</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -1403,7 +1394,7 @@
         <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K9">
         <v>957</v>
@@ -1415,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O9">
         <v>-84</v>
@@ -1427,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S9">
         <v>-84</v>
@@ -1442,19 +1433,19 @@
         <v>31</v>
       </c>
       <c r="W9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="X9">
-        <v>873</v>
+        <v>957</v>
       </c>
       <c r="Y9">
-        <v>37.5</v>
+        <v>44.900000000000013</v>
       </c>
       <c r="Z9" t="b">
         <v>1</v>
       </c>
       <c r="AA9">
-        <v>61.128526645768019</v>
+        <v>3.970741901776385</v>
       </c>
       <c r="AB9">
         <v>108.7774294670846</v>
@@ -1463,7 +1454,7 @@
         <v>108.7774294670846</v>
       </c>
       <c r="AD9">
-        <v>8.7774294670846391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
@@ -1471,22 +1462,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="D10">
-        <v>37.700000000000003</v>
+        <v>54</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>270.98008252509362</v>
+        <v>352.88365143405781</v>
       </c>
       <c r="G10">
-        <v>168.24450480754811</v>
+        <v>69.673008272454439</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -1495,7 +1486,7 @@
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K10">
         <v>642</v>
@@ -1507,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O10">
         <v>-214</v>
@@ -1519,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="S10">
         <v>-25</v>
@@ -1537,16 +1528,16 @@
         <v>66</v>
       </c>
       <c r="X10">
-        <v>642</v>
+        <v>557</v>
       </c>
       <c r="Y10">
-        <v>48.6</v>
+        <v>39.5</v>
       </c>
       <c r="Z10" t="b">
         <v>1</v>
       </c>
       <c r="AA10">
-        <v>57.476635514018703</v>
+        <v>43.457943925233643</v>
       </c>
       <c r="AB10">
         <v>133.33333333333329</v>
@@ -1555,7 +1546,7 @@
         <v>103.8940809968847</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>13.2398753894081</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
@@ -1563,22 +1554,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>384</v>
+        <v>895</v>
       </c>
       <c r="D11">
-        <v>37.700000000000003</v>
+        <v>46.1</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>419.03054174660872</v>
+        <v>904.27129887393926</v>
       </c>
       <c r="G11">
-        <v>162.59709968702509</v>
+        <v>62.660779197346052</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -1587,7 +1578,7 @@
         <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K11">
         <v>926</v>
@@ -1599,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O11">
         <v>-104</v>
@@ -1611,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S11">
         <v>-104</v>
@@ -1626,7 +1617,7 @@
         <v>31</v>
       </c>
       <c r="W11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X11">
         <v>895</v>
@@ -1638,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="AA11">
-        <v>58.53131749460043</v>
+        <v>3.3477321814254859</v>
       </c>
       <c r="AB11">
         <v>111.231101511879</v>
@@ -1662,28 +1653,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1694,7 +1685,7 @@
         <v>1292.8</v>
       </c>
       <c r="C2">
-        <v>480.9</v>
+        <v>1087.9000000000001</v>
       </c>
       <c r="D2">
         <v>373.1</v>
@@ -1703,13 +1694,13 @@
         <v>497.3</v>
       </c>
       <c r="F2">
-        <v>1172.4000000000001</v>
+        <v>1217.0999999999999</v>
       </c>
       <c r="G2">
-        <v>734.10739898681641</v>
+        <v>1644.667635679245</v>
       </c>
       <c r="H2">
-        <v>63.561973728807587</v>
+        <v>17.18506710724682</v>
       </c>
     </row>
   </sheetData>
